--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/38.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/38.xlsx
@@ -426,13 +426,13 @@
         <v>-10.70623438740811</v>
       </c>
       <c r="E2">
-        <v>-17.2741695867247</v>
+        <v>-15.11617964005748</v>
       </c>
       <c r="F2">
-        <v>-3.767094516994776</v>
+        <v>-4.074944008366767</v>
       </c>
       <c r="G2">
-        <v>-11.2207476487464</v>
+        <v>-10.45536938334014</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.12938120383303</v>
       </c>
       <c r="E3">
-        <v>-17.96941714417431</v>
+        <v>-15.61045352104668</v>
       </c>
       <c r="F3">
-        <v>-4.300158881105092</v>
+        <v>-4.236946992964864</v>
       </c>
       <c r="G3">
-        <v>-11.57257587593244</v>
+        <v>-9.383984151556881</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.400361453785949</v>
       </c>
       <c r="E4">
-        <v>-17.35832674768324</v>
+        <v>-16.39454068157877</v>
       </c>
       <c r="F4">
-        <v>-4.193274635121871</v>
+        <v>-4.150857253894119</v>
       </c>
       <c r="G4">
-        <v>-11.18443096418059</v>
+        <v>-9.382934708620931</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.579721895130199</v>
       </c>
       <c r="E5">
-        <v>-18.59840406994369</v>
+        <v>-16.75545100304209</v>
       </c>
       <c r="F5">
-        <v>-4.250042653235721</v>
+        <v>-4.417285061656525</v>
       </c>
       <c r="G5">
-        <v>-9.91908086925144</v>
+        <v>-8.991889758976679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.67549889519236</v>
       </c>
       <c r="E6">
-        <v>-19.21071715441683</v>
+        <v>-17.92156023086125</v>
       </c>
       <c r="F6">
-        <v>-3.925258018680897</v>
+        <v>-4.016226013386727</v>
       </c>
       <c r="G6">
-        <v>-9.715671019682</v>
+        <v>-8.102564668580104</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.729694683126533</v>
       </c>
       <c r="E7">
-        <v>-19.42446565605288</v>
+        <v>-17.75156584508731</v>
       </c>
       <c r="F7">
-        <v>-3.799667580007658</v>
+        <v>-3.759677315270109</v>
       </c>
       <c r="G7">
-        <v>-10.09862499602827</v>
+        <v>-8.406823666912361</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.765669471680007</v>
       </c>
       <c r="E8">
-        <v>-19.56349886503638</v>
+        <v>-18.29663109054655</v>
       </c>
       <c r="F8">
-        <v>-3.818859195995717</v>
+        <v>-3.796085719357953</v>
       </c>
       <c r="G8">
-        <v>-10.81979092575757</v>
+        <v>-7.853605022935832</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.806449957661966</v>
       </c>
       <c r="E9">
-        <v>-19.99745347224341</v>
+        <v>-18.62329256308985</v>
       </c>
       <c r="F9">
-        <v>-3.96840684832532</v>
+        <v>-3.914456107748391</v>
       </c>
       <c r="G9">
-        <v>-9.717266702631928</v>
+        <v>-7.973387181637742</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.872760509402931</v>
       </c>
       <c r="E10">
-        <v>-20.23563309115084</v>
+        <v>-19.80889234303802</v>
       </c>
       <c r="F10">
-        <v>-3.609592880863492</v>
+        <v>-3.767234511085849</v>
       </c>
       <c r="G10">
-        <v>-9.157705053402156</v>
+        <v>-7.302852735386059</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.988775612276598</v>
       </c>
       <c r="E11">
-        <v>-21.36990261822207</v>
+        <v>-20.3196815687332</v>
       </c>
       <c r="F11">
-        <v>-3.892602118927734</v>
+        <v>-3.687750173685028</v>
       </c>
       <c r="G11">
-        <v>-9.536765828194246</v>
+        <v>-7.176916272526644</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.168387162212082</v>
       </c>
       <c r="E12">
-        <v>-22.90864638671041</v>
+        <v>-20.62744571924249</v>
       </c>
       <c r="F12">
-        <v>-3.226304798485952</v>
+        <v>-3.708574501824005</v>
       </c>
       <c r="G12">
-        <v>-8.22767680560024</v>
+        <v>-6.686670825798131</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.421811501501488</v>
       </c>
       <c r="E13">
-        <v>-23.11940609550139</v>
+        <v>-21.18731907470681</v>
       </c>
       <c r="F13">
-        <v>-3.462068930098928</v>
+        <v>-3.525148279454708</v>
       </c>
       <c r="G13">
-        <v>-8.364716838198371</v>
+        <v>-6.666284486367299</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.772590553412795</v>
       </c>
       <c r="E14">
-        <v>-22.22807561351965</v>
+        <v>-22.00551922993868</v>
       </c>
       <c r="F14">
-        <v>-3.368431107253874</v>
+        <v>-3.158708361682707</v>
       </c>
       <c r="G14">
-        <v>-8.036830476352335</v>
+        <v>-6.189003135970572</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.2336134963932866</v>
       </c>
       <c r="E15">
-        <v>-23.62210293814486</v>
+        <v>-21.80886571768159</v>
       </c>
       <c r="F15">
-        <v>-3.427764579214195</v>
+        <v>-3.045602248137059</v>
       </c>
       <c r="G15">
-        <v>-6.735223286677082</v>
+        <v>-6.072697050084897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.1869671970402841</v>
       </c>
       <c r="E16">
-        <v>-24.29737992522065</v>
+        <v>-23.50054058188296</v>
       </c>
       <c r="F16">
-        <v>-3.00546370563441</v>
+        <v>-2.762322962299504</v>
       </c>
       <c r="G16">
-        <v>-7.301488790623879</v>
+        <v>-5.217291809283693</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.4785444620084143</v>
       </c>
       <c r="E17">
-        <v>-25.21728054971679</v>
+        <v>-23.57903262185791</v>
       </c>
       <c r="F17">
-        <v>-3.070851714941791</v>
+        <v>-2.75228480611238</v>
       </c>
       <c r="G17">
-        <v>-5.928416854392379</v>
+        <v>-4.915456130286182</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.6423673629529252</v>
       </c>
       <c r="E18">
-        <v>-25.64056154368774</v>
+        <v>-24.93665101546145</v>
       </c>
       <c r="F18">
-        <v>-2.475108931298651</v>
+        <v>-2.189768667362931</v>
       </c>
       <c r="G18">
-        <v>-5.984232652184492</v>
+        <v>-4.856266886589553</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.6930960819829768</v>
       </c>
       <c r="E19">
-        <v>-26.40466454842398</v>
+        <v>-25.08621745498679</v>
       </c>
       <c r="F19">
-        <v>-2.009744549916931</v>
+        <v>-2.714107009252156</v>
       </c>
       <c r="G19">
-        <v>-6.773695136388953</v>
+        <v>-4.58791075463069</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.652211036257253</v>
       </c>
       <c r="E20">
-        <v>-27.67593852812328</v>
+        <v>-25.82868793938839</v>
       </c>
       <c r="F20">
-        <v>-1.901409004244006</v>
+        <v>-1.810719340985516</v>
       </c>
       <c r="G20">
-        <v>-5.63520845707021</v>
+        <v>-3.473773137753287</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5455645088496656</v>
       </c>
       <c r="E21">
-        <v>-28.88668945271005</v>
+        <v>-26.5192666401361</v>
       </c>
       <c r="F21">
-        <v>-1.836754928455505</v>
+        <v>-1.499181129568859</v>
       </c>
       <c r="G21">
-        <v>-5.509295168029569</v>
+        <v>-4.796256627599184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4053331225494201</v>
       </c>
       <c r="E22">
-        <v>-28.68296246405298</v>
+        <v>-27.18679540818476</v>
       </c>
       <c r="F22">
-        <v>-1.554253479609178</v>
+        <v>-1.307224379685532</v>
       </c>
       <c r="G22">
-        <v>-5.216530383809661</v>
+        <v>-3.800123406469101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.2626687379139558</v>
       </c>
       <c r="E23">
-        <v>-28.4009472167513</v>
+        <v>-26.75537221794801</v>
       </c>
       <c r="F23">
-        <v>-1.925983351615456</v>
+        <v>-0.7664628256684035</v>
       </c>
       <c r="G23">
-        <v>-5.800560275120187</v>
+        <v>-4.627418805096353</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.1442082787910559</v>
       </c>
       <c r="E24">
-        <v>-30.34546263445993</v>
+        <v>-27.57849482442623</v>
       </c>
       <c r="F24">
-        <v>-1.809030299851208</v>
+        <v>-0.9020475170564182</v>
       </c>
       <c r="G24">
-        <v>-6.033695513086743</v>
+        <v>-4.528102438918218</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.07504170278193047</v>
       </c>
       <c r="E25">
-        <v>-30.83318834203405</v>
+        <v>-28.91282780468233</v>
       </c>
       <c r="F25">
-        <v>-1.512009227168612</v>
+        <v>-0.7626987241900826</v>
       </c>
       <c r="G25">
-        <v>-5.022817122124747</v>
+        <v>-4.090991248095007</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.07328160433265231</v>
       </c>
       <c r="E26">
-        <v>-30.93844592763133</v>
+        <v>-28.82020692580344</v>
       </c>
       <c r="F26">
-        <v>-1.376118868208964</v>
+        <v>-0.7793099757184211</v>
       </c>
       <c r="G26">
-        <v>-5.524603130603158</v>
+        <v>-4.220903676147087</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.1488660369764341</v>
       </c>
       <c r="E27">
-        <v>-28.76443876839899</v>
+        <v>-28.71059068397378</v>
       </c>
       <c r="F27">
-        <v>-1.64052297440633</v>
+        <v>-0.7668811512068172</v>
       </c>
       <c r="G27">
-        <v>-6.683307311530231</v>
+        <v>-5.546985728994171</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.3093342323813353</v>
       </c>
       <c r="E28">
-        <v>-31.85946055673335</v>
+        <v>-29.58081621284277</v>
       </c>
       <c r="F28">
-        <v>-0.9541551401621183</v>
+        <v>-0.6477113882726776</v>
       </c>
       <c r="G28">
-        <v>-6.368140065646075</v>
+        <v>-4.635483294030018</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.5551813642571712</v>
       </c>
       <c r="E29">
-        <v>-30.33628568188339</v>
+        <v>-29.06106287284941</v>
       </c>
       <c r="F29">
-        <v>-1.082842016187022</v>
+        <v>-0.6949821741134313</v>
       </c>
       <c r="G29">
-        <v>-4.778154564590449</v>
+        <v>-5.20376823075577</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.8769668013592601</v>
       </c>
       <c r="E30">
-        <v>-30.62356754445599</v>
+        <v>-28.69116805895488</v>
       </c>
       <c r="F30">
-        <v>-1.111229338713558</v>
+        <v>-0.6251135255243071</v>
       </c>
       <c r="G30">
-        <v>-6.378846369920078</v>
+        <v>-4.972675599386945</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.268001364672527</v>
       </c>
       <c r="E31">
-        <v>-30.09092390319979</v>
+        <v>-27.74285578853462</v>
       </c>
       <c r="F31">
-        <v>-0.7947524008414094</v>
+        <v>-0.6912909689665567</v>
       </c>
       <c r="G31">
-        <v>-6.976538882671177</v>
+        <v>-5.040852974222696</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.716585524752792</v>
       </c>
       <c r="E32">
-        <v>-30.03607049754488</v>
+        <v>-28.5745190969913</v>
       </c>
       <c r="F32">
-        <v>-0.8334065089582428</v>
+        <v>-0.4758599436226977</v>
       </c>
       <c r="G32">
-        <v>-6.801354744369563</v>
+        <v>-5.833917331973884</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.205128057083031</v>
       </c>
       <c r="E33">
-        <v>-29.72140042417389</v>
+        <v>-27.8946321233757</v>
       </c>
       <c r="F33">
-        <v>-1.298680598293058</v>
+        <v>-0.7105645933274929</v>
       </c>
       <c r="G33">
-        <v>-5.95735102240561</v>
+        <v>-5.838373326269743</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.717085888205204</v>
       </c>
       <c r="E34">
-        <v>-29.72732366817592</v>
+        <v>-27.77920584939419</v>
       </c>
       <c r="F34">
-        <v>-1.400070283293509</v>
+        <v>-0.9511382260811225</v>
       </c>
       <c r="G34">
-        <v>-6.179707124096298</v>
+        <v>-5.292550441027945</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.238708744667851</v>
       </c>
       <c r="E35">
-        <v>-28.58629765788525</v>
+        <v>-27.21602217943027</v>
       </c>
       <c r="F35">
-        <v>-1.434519598473732</v>
+        <v>-0.6858096618622325</v>
       </c>
       <c r="G35">
-        <v>-7.105431662697161</v>
+        <v>-5.438214444755877</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.754257828458907</v>
       </c>
       <c r="E36">
-        <v>-30.38843332431872</v>
+        <v>-27.01325975573683</v>
       </c>
       <c r="F36">
-        <v>-1.585258443128561</v>
+        <v>-0.7717378692894308</v>
       </c>
       <c r="G36">
-        <v>-6.283588732573089</v>
+        <v>-5.719941870147855</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.246118956306228</v>
       </c>
       <c r="E37">
-        <v>-27.27098426846136</v>
+        <v>-26.4403353381824</v>
       </c>
       <c r="F37">
-        <v>-1.415552470051832</v>
+        <v>-0.6284907794255207</v>
       </c>
       <c r="G37">
-        <v>-6.008247349526365</v>
+        <v>-5.80858834805292</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.705934252068838</v>
       </c>
       <c r="E38">
-        <v>-27.70555474813344</v>
+        <v>-25.56788859281265</v>
       </c>
       <c r="F38">
-        <v>-1.199351891390772</v>
+        <v>-0.5982363167730743</v>
       </c>
       <c r="G38">
-        <v>-5.635380605438251</v>
+        <v>-5.544701452572074</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.124945257430581</v>
       </c>
       <c r="E39">
-        <v>-25.98557692138413</v>
+        <v>-25.69038381472013</v>
       </c>
       <c r="F39">
-        <v>-1.944378078162022</v>
+        <v>-0.7383447225477771</v>
       </c>
       <c r="G39">
-        <v>-6.745512462213137</v>
+        <v>-4.831219299039427</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.491101338934132</v>
       </c>
       <c r="E40">
-        <v>-25.78529157297288</v>
+        <v>-25.01054665431862</v>
       </c>
       <c r="F40">
-        <v>-1.416433024601008</v>
+        <v>-0.902775652003479</v>
       </c>
       <c r="G40">
-        <v>-7.24311725167545</v>
+        <v>-5.388761515490244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.801499799895202</v>
       </c>
       <c r="E41">
-        <v>-26.51646804319936</v>
+        <v>-24.53605314779492</v>
       </c>
       <c r="F41">
-        <v>-1.619621608098893</v>
+        <v>-0.6318233014869831</v>
       </c>
       <c r="G41">
-        <v>-6.759158530926013</v>
+        <v>-5.133879303876216</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.054040941104177</v>
       </c>
       <c r="E42">
-        <v>-25.50696703198746</v>
+        <v>-23.84146221907642</v>
       </c>
       <c r="F42">
-        <v>-1.29861018706382</v>
+        <v>-0.6367719683513073</v>
       </c>
       <c r="G42">
-        <v>-6.079020192064904</v>
+        <v>-5.513714746324496</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.244483151926463</v>
       </c>
       <c r="E43">
-        <v>-25.01890168886277</v>
+        <v>-23.72750317067339</v>
       </c>
       <c r="F43">
-        <v>-1.483228430125746</v>
+        <v>-0.9101878835237289</v>
       </c>
       <c r="G43">
-        <v>-6.173397224298448</v>
+        <v>-5.276643269711747</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.37196483541156</v>
       </c>
       <c r="E44">
-        <v>-25.00426566086998</v>
+        <v>-23.3339606655108</v>
       </c>
       <c r="F44">
-        <v>-1.631543471759983</v>
+        <v>-1.010684588463962</v>
       </c>
       <c r="G44">
-        <v>-6.463563230270028</v>
+        <v>-5.001728947039589</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.440060615668489</v>
       </c>
       <c r="E45">
-        <v>-24.25257520338876</v>
+        <v>-22.63447445639001</v>
       </c>
       <c r="F45">
-        <v>-1.553459903637296</v>
+        <v>-0.6691420813505036</v>
       </c>
       <c r="G45">
-        <v>-6.382444932921266</v>
+        <v>-4.904690236192472</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.449946067160948</v>
       </c>
       <c r="E46">
-        <v>-22.6023494617796</v>
+        <v>-21.93820346381466</v>
       </c>
       <c r="F46">
-        <v>-1.493333684072497</v>
+        <v>-0.8587280437270181</v>
       </c>
       <c r="G46">
-        <v>-6.549998263754859</v>
+        <v>-5.328158668848346</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.401826678870497</v>
       </c>
       <c r="E47">
-        <v>-22.58592468655378</v>
+        <v>-20.90877716696902</v>
       </c>
       <c r="F47">
-        <v>-1.249966796436627</v>
+        <v>-0.7443785507097687</v>
       </c>
       <c r="G47">
-        <v>-6.109963861220472</v>
+        <v>-5.051622178861945</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.304047106524751</v>
       </c>
       <c r="E48">
-        <v>-22.16712235337641</v>
+        <v>-21.29530959436773</v>
       </c>
       <c r="F48">
-        <v>-1.168233441537206</v>
+        <v>-0.8796749702416091</v>
       </c>
       <c r="G48">
-        <v>-6.783918101014222</v>
+        <v>-5.29761557570303</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.160865049405789</v>
       </c>
       <c r="E49">
-        <v>-21.69950307039635</v>
+        <v>-20.39990801425309</v>
       </c>
       <c r="F49">
-        <v>-1.51413316118939</v>
+        <v>-1.135970187932971</v>
       </c>
       <c r="G49">
-        <v>-5.110112897449788</v>
+        <v>-4.903339533612449</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.97208518787853</v>
       </c>
       <c r="E50">
-        <v>-20.8379835328071</v>
+        <v>-19.72673676759087</v>
       </c>
       <c r="F50">
-        <v>-1.277445399922293</v>
+        <v>-0.9428893434840451</v>
       </c>
       <c r="G50">
-        <v>-6.433526650592221</v>
+        <v>-4.927758117510114</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.746185535742183</v>
       </c>
       <c r="E51">
-        <v>-22.27996286869954</v>
+        <v>-20.4150874591268</v>
       </c>
       <c r="F51">
-        <v>-1.325694487665753</v>
+        <v>-0.8323652511329238</v>
       </c>
       <c r="G51">
-        <v>-7.067254451538286</v>
+        <v>-4.956490342245448</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.486111248192357</v>
       </c>
       <c r="E52">
-        <v>-21.105955982211</v>
+        <v>-19.01869627106958</v>
       </c>
       <c r="F52">
-        <v>-1.012312330410463</v>
+        <v>-0.9185320283721283</v>
       </c>
       <c r="G52">
-        <v>-5.791731050166951</v>
+        <v>-4.75680154586215</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.190735044167743</v>
       </c>
       <c r="E53">
-        <v>-18.17987344520678</v>
+        <v>-17.21410390748695</v>
       </c>
       <c r="F53">
-        <v>-1.410581437267632</v>
+        <v>-1.015760823908318</v>
       </c>
       <c r="G53">
-        <v>-5.777396387981907</v>
+        <v>-5.229650075781793</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.863673811845926</v>
       </c>
       <c r="E54">
-        <v>-19.76813607696899</v>
+        <v>-18.42729567956387</v>
       </c>
       <c r="F54">
-        <v>-1.503897853560399</v>
+        <v>-1.10394798924295</v>
       </c>
       <c r="G54">
-        <v>-7.197822367607142</v>
+        <v>-5.469376609917037</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.50878290707288</v>
       </c>
       <c r="E55">
-        <v>-19.47047948044482</v>
+        <v>-17.77973295341502</v>
       </c>
       <c r="F55">
-        <v>-1.869255923504343</v>
+        <v>-1.035901748939985</v>
       </c>
       <c r="G55">
-        <v>-6.663556596842939</v>
+        <v>-5.2173513991034</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.12656917275979</v>
       </c>
       <c r="E56">
-        <v>-16.8281964095013</v>
+        <v>-17.10569676821734</v>
       </c>
       <c r="F56">
-        <v>-1.180767468708965</v>
+        <v>-0.9957482958240843</v>
       </c>
       <c r="G56">
-        <v>-7.119412096509503</v>
+        <v>-5.007826971922927</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.719320976525903</v>
       </c>
       <c r="E57">
-        <v>-18.86362773562493</v>
+        <v>-17.04759644669892</v>
       </c>
       <c r="F57">
-        <v>-1.698562536483477</v>
+        <v>-1.276728033751468</v>
       </c>
       <c r="G57">
-        <v>-6.453820294747953</v>
+        <v>-5.053535674183644</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.295832058636447</v>
       </c>
       <c r="E58">
-        <v>-17.7852712771264</v>
+        <v>-16.46351839766361</v>
       </c>
       <c r="F58">
-        <v>-1.837356323189937</v>
+        <v>-1.192670279919791</v>
       </c>
       <c r="G58">
-        <v>-6.269998943134381</v>
+        <v>-5.383640101540991</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.861434521294777</v>
       </c>
       <c r="E59">
-        <v>-18.13144594416875</v>
+        <v>-16.228187188907</v>
       </c>
       <c r="F59">
-        <v>-2.169467039055121</v>
+        <v>-1.177419207666849</v>
       </c>
       <c r="G59">
-        <v>-7.081403723173131</v>
+        <v>-5.50088638235982</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.420717904774047</v>
       </c>
       <c r="E60">
-        <v>-17.18950070820328</v>
+        <v>-16.40516901007478</v>
       </c>
       <c r="F60">
-        <v>-2.078701994362976</v>
+        <v>-1.270299074338341</v>
       </c>
       <c r="G60">
-        <v>-7.112158691232961</v>
+        <v>-5.837439752427668</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.987516149935239</v>
       </c>
       <c r="E61">
-        <v>-16.94538425987179</v>
+        <v>-16.0553806207743</v>
       </c>
       <c r="F61">
-        <v>-1.789851109374191</v>
+        <v>-1.306228682067367</v>
       </c>
       <c r="G61">
-        <v>-7.415560258270546</v>
+        <v>-6.045649893029051</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.572331374486732</v>
       </c>
       <c r="E62">
-        <v>-16.59619362914033</v>
+        <v>-15.61364156674808</v>
       </c>
       <c r="F62">
-        <v>-1.572926537603085</v>
+        <v>-1.140247048833624</v>
       </c>
       <c r="G62">
-        <v>-7.336305798060395</v>
+        <v>-5.754752256493291</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.183983166270851</v>
       </c>
       <c r="E63">
-        <v>-17.6766377141564</v>
+        <v>-15.17902580233593</v>
       </c>
       <c r="F63">
-        <v>-1.661222219067484</v>
+        <v>-1.421630201686172</v>
       </c>
       <c r="G63">
-        <v>-6.907083637257267</v>
+        <v>-6.529370254499661</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.8345963860892467</v>
       </c>
       <c r="E64">
-        <v>-17.11858480524316</v>
+        <v>-14.79731619975538</v>
       </c>
       <c r="F64">
-        <v>-1.864858120962881</v>
+        <v>-1.9320917328437</v>
       </c>
       <c r="G64">
-        <v>-7.301922472089524</v>
+        <v>-6.12668873728487</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.5358422045085455</v>
       </c>
       <c r="E65">
-        <v>-15.78541564280703</v>
+        <v>-15.34868055255929</v>
       </c>
       <c r="F65">
-        <v>-1.948347614756237</v>
+        <v>-1.577478416481468</v>
       </c>
       <c r="G65">
-        <v>-7.369676097096248</v>
+        <v>-5.493666082538669</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.2953715903529489</v>
       </c>
       <c r="E66">
-        <v>-17.08398273535056</v>
+        <v>-15.23910053852168</v>
       </c>
       <c r="F66">
-        <v>-1.916316304024786</v>
+        <v>-1.498517607279216</v>
       </c>
       <c r="G66">
-        <v>-8.261053725727173</v>
+        <v>-5.967650129578282</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.1178411924845849</v>
       </c>
       <c r="E67">
-        <v>-14.81951477934098</v>
+        <v>-14.33887160511487</v>
       </c>
       <c r="F67">
-        <v>-1.57295470209478</v>
+        <v>-1.690201824287022</v>
       </c>
       <c r="G67">
-        <v>-8.382918217573284</v>
+        <v>-6.378078323354967</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.01084130989842546</v>
       </c>
       <c r="E68">
-        <v>-17.00756020799711</v>
+        <v>-15.3975699579461</v>
       </c>
       <c r="F68">
-        <v>-1.957792659882957</v>
+        <v>-1.666450874113954</v>
       </c>
       <c r="G68">
-        <v>-8.609664102649045</v>
+        <v>-6.427769611899428</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.02446554124975767</v>
       </c>
       <c r="E69">
-        <v>-15.80760969391863</v>
+        <v>-14.85316134121797</v>
       </c>
       <c r="F69">
-        <v>-1.88150499228954</v>
+        <v>-1.462352743207795</v>
       </c>
       <c r="G69">
-        <v>-7.242792818212601</v>
+        <v>-6.2663672746778</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.007991846653252156</v>
       </c>
       <c r="E70">
-        <v>-16.11452249131448</v>
+        <v>-14.29562014986761</v>
       </c>
       <c r="F70">
-        <v>-1.248626497978898</v>
+        <v>-1.768692120804483</v>
       </c>
       <c r="G70">
-        <v>-8.772043050804758</v>
+        <v>-6.003198767578977</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.1046980638943104</v>
       </c>
       <c r="E71">
-        <v>-14.96994615740179</v>
+        <v>-14.42566886641989</v>
       </c>
       <c r="F71">
-        <v>-2.470179316884591</v>
+        <v>-1.832397715916779</v>
       </c>
       <c r="G71">
-        <v>-7.718968446399212</v>
+        <v>-6.287995068685859</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.2593337350700796</v>
       </c>
       <c r="E72">
-        <v>-16.65556192338089</v>
+        <v>-14.65992682683667</v>
       </c>
       <c r="F72">
-        <v>-2.272030520665338</v>
+        <v>-2.132988223738039</v>
       </c>
       <c r="G72">
-        <v>-7.216656061180055</v>
+        <v>-6.245120193406758</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.4623630353823189</v>
       </c>
       <c r="E73">
-        <v>-16.34726341293869</v>
+        <v>-14.70375792675691</v>
       </c>
       <c r="F73">
-        <v>-2.309309538893525</v>
+        <v>-1.822986633853574</v>
       </c>
       <c r="G73">
-        <v>-7.822333609771876</v>
+        <v>-6.510013494731542</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.7020532872976231</v>
       </c>
       <c r="E74">
-        <v>-16.15406965482346</v>
+        <v>-14.90604486067955</v>
       </c>
       <c r="F74">
-        <v>-2.061872882207701</v>
+        <v>-1.956974232888991</v>
       </c>
       <c r="G74">
-        <v>-6.934865735422831</v>
+        <v>-6.124172722675024</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.9705333257377098</v>
       </c>
       <c r="E75">
-        <v>-16.54707780005314</v>
+        <v>-16.11191861876006</v>
       </c>
       <c r="F75">
-        <v>-2.260565087443191</v>
+        <v>-2.00008330089808</v>
       </c>
       <c r="G75">
-        <v>-7.390168373984337</v>
+        <v>-5.330068853624505</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.259157341860305</v>
       </c>
       <c r="E76">
-        <v>-18.18376340437937</v>
+        <v>-15.68281853568925</v>
       </c>
       <c r="F76">
-        <v>-2.273977184061917</v>
+        <v>-2.031688830784493</v>
       </c>
       <c r="G76">
-        <v>-7.759525939800823</v>
+        <v>-6.136663410994695</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.557347187203793</v>
       </c>
       <c r="E77">
-        <v>-18.09102478517629</v>
+        <v>-15.82622625056416</v>
       </c>
       <c r="F77">
-        <v>-2.609933181410896</v>
+        <v>-2.089331604875699</v>
       </c>
       <c r="G77">
-        <v>-7.300310236411899</v>
+        <v>-5.290871994439534</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.860495570074343</v>
       </c>
       <c r="E78">
-        <v>-18.44707605402937</v>
+        <v>-16.73178972635201</v>
       </c>
       <c r="F78">
-        <v>-2.644092568000139</v>
+        <v>-2.171642331854872</v>
       </c>
       <c r="G78">
-        <v>-7.600884597558948</v>
+        <v>-5.4721806419888</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.165827736015003</v>
       </c>
       <c r="E79">
-        <v>-18.27657900764058</v>
+        <v>-16.89360568806809</v>
       </c>
       <c r="F79">
-        <v>-2.348223754374837</v>
+        <v>-2.148672532142645</v>
       </c>
       <c r="G79">
-        <v>-6.720646954667671</v>
+        <v>-5.559075841303589</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.470027819796806</v>
       </c>
       <c r="E80">
-        <v>-19.32670043070128</v>
+        <v>-17.57148201922428</v>
       </c>
       <c r="F80">
-        <v>-2.234721681210652</v>
+        <v>-2.405415068231518</v>
       </c>
       <c r="G80">
-        <v>-6.943291073820276</v>
+        <v>-5.740126266300791</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.770814807974769</v>
       </c>
       <c r="E81">
-        <v>-19.11463652139609</v>
+        <v>-19.1892114313544</v>
       </c>
       <c r="F81">
-        <v>-2.346043491370669</v>
+        <v>-2.392968848004455</v>
       </c>
       <c r="G81">
-        <v>-6.371427437366571</v>
+        <v>-4.819013317636133</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.07024526279906</v>
       </c>
       <c r="E82">
-        <v>-20.86486908299064</v>
+        <v>-19.14074770252432</v>
       </c>
       <c r="F82">
-        <v>-2.527370630741272</v>
+        <v>-2.096247644321672</v>
       </c>
       <c r="G82">
-        <v>-6.709924097665972</v>
+        <v>-4.567372130105052</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.367908625011304</v>
       </c>
       <c r="E83">
-        <v>-21.93744720865538</v>
+        <v>-19.73139656734476</v>
       </c>
       <c r="F83">
-        <v>-2.576611274265883</v>
+        <v>-2.50615117135116</v>
       </c>
       <c r="G83">
-        <v>-7.053442855548447</v>
+        <v>-5.311384134600859</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.658345149967923</v>
       </c>
       <c r="E84">
-        <v>-23.62294070583628</v>
+        <v>-20.60384331271452</v>
       </c>
       <c r="F84">
-        <v>-2.8481617060472</v>
+        <v>-2.294036100720708</v>
       </c>
       <c r="G84">
-        <v>-6.207254173528574</v>
+        <v>-4.47753054526031</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.940883552950134</v>
       </c>
       <c r="E85">
-        <v>-21.49140157584787</v>
+        <v>-21.88592223139611</v>
       </c>
       <c r="F85">
-        <v>-2.736996457326312</v>
+        <v>-2.668296635142538</v>
       </c>
       <c r="G85">
-        <v>-6.225372789265005</v>
+        <v>-4.698588913099605</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.210149673616349</v>
       </c>
       <c r="E86">
-        <v>-23.5665702613888</v>
+        <v>-22.92730369962201</v>
       </c>
       <c r="F86">
-        <v>-2.45629256574406</v>
+        <v>-2.455066581987917</v>
       </c>
       <c r="G86">
-        <v>-5.87844748002262</v>
+        <v>-4.177350139032435</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.454618485234088</v>
       </c>
       <c r="E87">
-        <v>-25.4120592737347</v>
+        <v>-24.63129148465023</v>
       </c>
       <c r="F87">
-        <v>-3.129176235405502</v>
+        <v>-2.582008087895122</v>
       </c>
       <c r="G87">
-        <v>-5.74494642060597</v>
+        <v>-4.577489157273065</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.664707850111015</v>
       </c>
       <c r="E88">
-        <v>-25.84773922953866</v>
+        <v>-25.46615642423033</v>
       </c>
       <c r="F88">
-        <v>-2.869379508702507</v>
+        <v>-2.327609831556171</v>
       </c>
       <c r="G88">
-        <v>-5.587043330019353</v>
+        <v>-4.279831386746114</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.828266289358347</v>
       </c>
       <c r="E89">
-        <v>-29.26709485477638</v>
+        <v>-26.75052675075981</v>
       </c>
       <c r="F89">
-        <v>-2.996568696463148</v>
+        <v>-2.640095695281632</v>
       </c>
       <c r="G89">
-        <v>-5.713535964529366</v>
+        <v>-4.414587142922148</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.930316185543155</v>
       </c>
       <c r="E90">
-        <v>-28.63842039371353</v>
+        <v>-28.37902940255417</v>
       </c>
       <c r="F90">
-        <v>-3.118154807111254</v>
+        <v>-2.618579680361317</v>
       </c>
       <c r="G90">
-        <v>-5.138699458181395</v>
+        <v>-4.051039584527082</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.958529681932445</v>
       </c>
       <c r="E91">
-        <v>-29.4331766390077</v>
+        <v>-29.860795911078</v>
       </c>
       <c r="F91">
-        <v>-2.686390664321888</v>
+        <v>-2.73304845828457</v>
       </c>
       <c r="G91">
-        <v>-4.886786805916094</v>
+        <v>-4.865006726813228</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.904958188013176</v>
       </c>
       <c r="E92">
-        <v>-32.24760059240479</v>
+        <v>-31.71196362982952</v>
       </c>
       <c r="F92">
-        <v>-3.175211097081279</v>
+        <v>-2.852021069776843</v>
       </c>
       <c r="G92">
-        <v>-5.69739043393434</v>
+        <v>-5.19064191769256</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.763051633260948</v>
       </c>
       <c r="E93">
-        <v>-34.82689711837561</v>
+        <v>-32.97000993695241</v>
       </c>
       <c r="F93">
-        <v>-3.222632645789342</v>
+        <v>-2.993596514221904</v>
       </c>
       <c r="G93">
-        <v>-5.817510268281255</v>
+        <v>-4.220681869595956</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.529865965082284</v>
       </c>
       <c r="E94">
-        <v>-35.42041024300591</v>
+        <v>-34.96720509279227</v>
       </c>
       <c r="F94">
-        <v>-3.177609220712383</v>
+        <v>-3.107069594526991</v>
       </c>
       <c r="G94">
-        <v>-6.255591448947473</v>
+        <v>-4.736471485705485</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.213644604163268</v>
       </c>
       <c r="E95">
-        <v>-37.62287659713946</v>
+        <v>-36.9572996013881</v>
       </c>
       <c r="F95">
-        <v>-3.315449556538221</v>
+        <v>-3.006001316078827</v>
       </c>
       <c r="G95">
-        <v>-6.518846030230318</v>
+        <v>-5.187609457978588</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.82035702115551</v>
       </c>
       <c r="E96">
-        <v>-38.39985631771651</v>
+        <v>-38.85969341811439</v>
       </c>
       <c r="F96">
-        <v>-3.088510022867268</v>
+        <v>-3.020955832801566</v>
       </c>
       <c r="G96">
-        <v>-6.736815659081472</v>
+        <v>-5.286270336139948</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.367514501096341</v>
       </c>
       <c r="E97">
-        <v>-41.44673363463833</v>
+        <v>-40.3609912350333</v>
       </c>
       <c r="F97">
-        <v>-3.418977257805297</v>
+        <v>-3.235345600320106</v>
       </c>
       <c r="G97">
-        <v>-6.79614394569075</v>
+        <v>-4.989986442011794</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.86612584814769</v>
       </c>
       <c r="E98">
-        <v>-43.85194429856929</v>
+        <v>-42.85830653180626</v>
       </c>
       <c r="F98">
-        <v>-4.00471336322262</v>
+        <v>-3.866738831877528</v>
       </c>
       <c r="G98">
-        <v>-7.731161185620348</v>
+        <v>-5.710933875735498</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.353716254530406</v>
       </c>
       <c r="E99">
-        <v>-45.80189841356114</v>
+        <v>-45.47827781131399</v>
       </c>
       <c r="F99">
-        <v>-4.099410667975854</v>
+        <v>-3.787658737769274</v>
       </c>
       <c r="G99">
-        <v>-6.729121951248206</v>
+        <v>-6.430676270882908</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.825765944481009</v>
       </c>
       <c r="E100">
-        <v>-47.65130455592367</v>
+        <v>-47.1227433339854</v>
       </c>
       <c r="F100">
-        <v>-4.058899360141944</v>
+        <v>-4.292591744880518</v>
       </c>
       <c r="G100">
-        <v>-7.612239768758648</v>
+        <v>-6.402857756716412</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.343698596685818</v>
       </c>
       <c r="E101">
-        <v>-49.23359073411426</v>
+        <v>-48.71067878350055</v>
       </c>
       <c r="F101">
-        <v>-4.478413605778711</v>
+        <v>-4.033683856400727</v>
       </c>
       <c r="G101">
-        <v>-7.60932317813855</v>
+        <v>-6.919885516857629</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.8633026066691679</v>
       </c>
       <c r="E102">
-        <v>-52.07623387329015</v>
+        <v>-52.04204502665074</v>
       </c>
       <c r="F102">
-        <v>-4.385286885621185</v>
+        <v>-4.380042491594062</v>
       </c>
       <c r="G102">
-        <v>-8.347717186854213</v>
+        <v>-7.08427396615568</v>
       </c>
     </row>
   </sheetData>
